--- a/sheets/대금율보/검수/궁초댕기 (b2_092_3).xlsx
+++ b/sheets/대금율보/검수/궁초댕기 (b2_092_3).xlsx
@@ -2347,8 +2347,7 @@
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="C4" s="23" t="inlineStr">
@@ -2442,8 +2441,7 @@
         <is>
           <t xml:space="preserve">淋㳞
 汰
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="G6" s="24" t="inlineStr">
@@ -2523,11 +2521,7 @@
           <t xml:space="preserve">짝에</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H8" s="21"/>
       <c r="I8" s="23"/>
     </row>
     <row r="9" ht="56" customHeight="1">
@@ -2713,8 +2707,7 @@
         <is>
           <t xml:space="preserve">南
 潢
-–
-‹</t>
+–</t>
         </is>
       </c>
       <c r="I14" s="24" t="inlineStr">

--- a/sheets/대금율보/검수/궁초댕기 (b2_092_3).xlsx
+++ b/sheets/대금율보/검수/궁초댕기 (b2_092_3).xlsx
@@ -2265,20 +2265,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="81.63" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="91.25" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="91.25" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="91.25" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
       <c r="H5" s="21"/>
       <c r="I5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="91.25" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
       <c r="H6" s="21"/>
       <c r="I6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="91.25" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
       <c r="H7" s="21"/>
       <c r="I7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="91.25" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
       <c r="H8" s="21"/>
       <c r="I8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="91.25" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="23"/>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="91.25" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="24"/>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="91.25" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="91.25" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="91.25" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="91.25" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -2716,7 +2716,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="91.25" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -2737,7 +2737,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="91.25" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -2764,7 +2764,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="91.25" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="91.25" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="24"/>
@@ -2832,6 +2832,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
 </worksheet>
 </file>